--- a/docs/AI问书-研发同步改动清单.xlsx
+++ b/docs/AI问书-研发同步改动清单.xlsx
@@ -1453,7 +1453,7 @@
       <c r="G2" s="2" t="n"/>
       <c r="H2" s="2" t="n"/>
     </row>
-    <row r="3" ht="232" customHeight="1">
+    <row r="3" ht="174" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
           <t>知识产品 KP</t>
@@ -1470,11 +1470,11 @@
             <rPr>
               <sz val="10"/>
             </rPr>
-            <t>（1）机构后台点「下架」时弹二次确认，弹窗里写清楚下架之后会发生什么——停止检索、停止新购、停止扫码与链接访问，并明确告诉运营「已购读者的权益不会清除，重新上架自动恢复」。
-（2）下架成功后，后台列表和详情里的状态标变成「已下架」（琥珀色），原来的「下架」按钮变成「重新发布」。
-（3）读者侧「我的纸书」里，这本书的卡片会在扫码时间后面挂一个灰色「已下架」小标，整张卡片降透明度，一眼能看出来暂时用不了。
-（4）如果读者之前已经解锁过，「已解锁」角标仍然保留（只是跟着变淡）——让读者知道钱没白花，只是暂时看不了。
-（5）点这张卡片不进会话，弹提示「该内容已下架，若有问题请联系客服」。</t>
+            <t>（1）机构后台点「下架」弹二次确认，弹窗列明：停止检索、停止新购、停止扫码与链接访问；已购权益不清除，重新上架自动恢复。
+（2）下架后状态标变「已下架」（琥珀色），「下架」按钮变「重新发布」。
+（3）读者端「我的纸书」卡片在扫码时间后挂灰色「已下架」标，整卡降透明度。
+（4）已解锁的书保留「已解锁」角标，同步变淡。
+（5）点击卡片不进会话，提示「该内容已下架，若有问题请联系客服」。</t>
           </r>
           <r>
             <rPr>
@@ -1482,16 +1482,16 @@
               <color rgb="00DC2626"/>
               <sz val="10"/>
             </rPr>
-            <t>已经买断永享的读者也一样被拦住</t>
+            <t>已买断永享的读者同样拦截</t>
           </r>
           <r>
             <rPr>
               <sz val="10"/>
             </rPr>
             <t>。
-（6）「我的永享」同理：封面置灰、副标题写「已下架」、点击拦截。
-（7）会话里引用了这本书的图音视频，那些卡片也会置灰并标「已下架」，点了只提示、不再弹付费墙（避免读者为看不了的内容付钱）。
-（8）读者扫这本书的二维码或点前台链接，会进到判活页提示已下架，停 3 秒后自动带他去这家机构最新的一本书。</t>
+（6）「我的永享」封面置灰、副标题写「已下架」、点击拦截。
+（7）会话内引用的图音视频置灰并标「已下架」，点击只提示、不弹付费墙。
+（8）扫码或点前台链接进判活页提示已下架，3 秒后跳转本机构最新已发布 KP。</t>
           </r>
         </is>
       </c>
@@ -1507,7 +1507,7 @@
       <c r="G3" s="6" t="n"/>
       <c r="H3" s="6" t="n"/>
     </row>
-    <row r="4" ht="217.5" customHeight="1">
+    <row r="4" ht="174" customHeight="1">
       <c r="A4" s="3" t="inlineStr">
         <is>
           <t>知识产品 KP</t>
@@ -1524,7 +1524,7 @@
             <rPr>
               <sz val="10"/>
             </rPr>
-            <t>（1）删除是</t>
+            <t>（1）删除为</t>
           </r>
           <r>
             <rPr>
@@ -1538,11 +1538,11 @@
             <rPr>
               <sz val="10"/>
             </rPr>
-            <t>——三端界面上都不再显示这本 KP，但数据库里所有数据完整保留（订单、权益、知识文件、二维码、分享记录）。界面上不再出现「彻底删除 / 永久删除」这类说法。
-（2）点删除弹二次确认，弹窗分两种：这本 KP 没人买过也没被分享过的，只做简单确认；已经产生业务关系的，会列出具体影响，并写明「本 KP 有 N 位已购永享用户、M 位纸书扫码解锁用户」。
-（3）删除后，机构后台和平台超管的列表里都不再展示它，筛选项里也没有「已删除」这一档——平台超管也看不到。
-（4）读者侧「我的纸书」「我的永享」里的记录保留，但标成「已失效」，点击拦截并提示「该内容已失效，若有问题请联系客服」。
-（5）历史会话里引用过的内容同样标「已失效」，不再可点。
+            <t>：三端界面不再展示，数据库保留全部数据（订单、权益、知识文件、二维码、分享记录）。界面文案不再出现「彻底删除 / 永久删除」。
+（2）删除弹二次确认，分两种：无业务关系的简单确认；有业务关系的列明影响，并写明「本 KP 有 N 位已购永享用户、M 位纸书扫码解锁用户」。
+（3）删除后两个后台列表均不展示，筛选项无「已删除」档。
+（4）读者端「我的纸书」「我的永享」记录保留并标「已失效」，点击拦截并提示「该内容已失效，若有问题请联系客服」。
+（5）历史会话引用的内容同标「已失效」，不可点击。
 （6）</t>
           </r>
           <r>
@@ -1557,8 +1557,8 @@
             <rPr>
               <sz val="10"/>
             </rPr>
-            <t>——这是数据留着的主要原因：读者来投诉时，客服要能查到他买过什么、什么时候买的、该退多少钱。
-（7）读者扫已删除 KP 的码，判活页提示「已失效」，3 秒后带去这家机构最新的一本书。</t>
+            <t>。
+（7）扫已删除 KP 的码，判活页提示「已失效」，3 秒后跳转本机构最新已发布 KP。</t>
           </r>
         </is>
       </c>
@@ -1574,7 +1574,7 @@
       <c r="G4" s="6" t="n"/>
       <c r="H4" s="6" t="n"/>
     </row>
-    <row r="5" ht="217.5" customHeight="1">
+    <row r="5" ht="145" customHeight="1">
       <c r="A5" s="3" t="inlineStr">
         <is>
           <t>知识产品 KP</t>
@@ -1591,7 +1591,7 @@
             <rPr>
               <sz val="10"/>
             </rPr>
-            <t>（1）两个后台的状态叫法统一成三个：</t>
+            <t>（1）两个后台状态命名统一为</t>
           </r>
           <r>
             <rPr>
@@ -1605,9 +1605,9 @@
             <rPr>
               <sz val="10"/>
             </rPr>
-            <t>（原来机构后台叫「未发 / 已发」，平台后台是另一套）。
-（2）配色也统一：草稿灰色描边、已发布绿色、已下架琥珀色，列表和详情页同色。
-（3）状态操作按钮跟着当前状态走，</t>
+            <t>。
+（2）配色统一：草稿灰色描边、已发布绿色、已下架琥珀色，列表与详情页同色。
+（3）状态操作按钮随当前状态变，</t>
           </r>
           <r>
             <rPr>
@@ -1621,11 +1621,10 @@
             <rPr>
               <sz val="10"/>
             </rPr>
-            <t>——草稿只有「发布」，已发布只有「下架」，已下架只有「重新发布」。原来是固定摆两个按钮，而且点了不生效。
-（4）「发布」也要二次确认，弹窗说明发布后前台立即可见，并提示「发布需至少一份已向量化完成的知识内容」。
-（5）来源标签也是三种：自建 / 分享导入·实时 / 分享导入·快照，统一用灰色，不跟状态标抢颜色。
-（6）原来的「归档」状态取消了、并入删除——运营反馈分不清归档和删除的区别。
-（7）测试注意：按按钮文字定位的自动化脚本要全改；另外状态会存在浏览器本地，跨轮次测试前记得清一下缓存。</t>
+            <t>：草稿→「发布」，已发布→「下架」，已下架→「重新发布」。
+（4）「发布」加二次确认，说明发布后前台立即可见，并提示「发布需至少一份已向量化完成的知识内容」。
+（5）来源标签三种：自建 / 分享导入·实时 / 分享导入·快照，统一灰色。
+（6）取消「归档」状态，并入删除。</t>
           </r>
         </is>
       </c>
@@ -1640,7 +1639,7 @@
       <c r="G5" s="6" t="n"/>
       <c r="H5" s="6" t="n"/>
     </row>
-    <row r="6" ht="188.5" customHeight="1">
+    <row r="6" ht="145" customHeight="1">
       <c r="A6" s="3" t="inlineStr">
         <is>
           <t>知识产品 KP</t>
@@ -1657,10 +1656,10 @@
             <rPr>
               <sz val="10"/>
             </rPr>
-            <t>（1）新增了一个统一的入口页。以前扫码或点前台链接直接进会话、不检查这本书还在不在，现在所有前台入口都先过这一道。
-（2）正常的（已发布）直接进会话，读者无感知。
-（3）已下架的，整屏提示「该知识 KP 已下架，若有问题请联系客服」。
-（4）已删除的、还是草稿的、或者链接本身就是错的，统一提示「已失效」——</t>
+            <t>（1）新增统一判活入口页，所有前台入口（扫码、前台链接）先经此页校验。
+（2）已发布：直接进会话。
+（3）已下架：整屏提示「该知识 KP 已下架，若有问题请联系客服」。
+（4）已删除、草稿、链接不存在：统一提示「已失效」。</t>
           </r>
           <r>
             <rPr>
@@ -1668,17 +1667,17 @@
               <color rgb="00DC2626"/>
               <sz val="10"/>
             </rPr>
-            <t>草稿也按失效处理</t>
-          </r>
-          <r>
-            <rPr>
-              <sz val="10"/>
-            </rPr>
-            <t>，是为了不让外面的人通过链接猜到这家机构在准备什么书。
-（5）提示停留 3 秒，然后自动带读者去这家机构最新发布的一本书开新会话，不让他空着手走。
-（6）如果读者还没登录，会先去登录页，登录完再进。
-（7）如果这家机构一本已发布的书都没有，就停在提示页不跳转，副标题说明「本机构暂无可进入的知识 KP」。
-（8）前台访问地址换了形态：从带参数的链接改成机构自己的二级域名加路径，机构后台可一键复制。</t>
+            <t>草稿按失效处理，不对外暴露未发布内容</t>
+          </r>
+          <r>
+            <rPr>
+              <sz val="10"/>
+            </rPr>
+            <t>。
+（5）提示停留 3 秒后跳转本机构最新已发布 KP 的新会话。
+（6）未登录先跳登录页，登录后再进。
+（7）该机构无已发布 KP 时停留本页，提示「本机构暂无可进入的知识 KP」。
+（8）前台访问地址改为机构二级域名 + 路径，机构后台可一键复制。</t>
           </r>
         </is>
       </c>
@@ -1707,7 +1706,7 @@
       <c r="G7" s="7" t="n"/>
       <c r="H7" s="7" t="n"/>
     </row>
-    <row r="8" ht="232" customHeight="1">
+    <row r="8" ht="117" customHeight="1">
       <c r="A8" s="8" t="inlineStr">
         <is>
           <t>会员与付费</t>
@@ -1720,46 +1719,10 @@
       </c>
       <c r="C8" s="8" t="inlineStr">
         <is>
-          <r>
-            <rPr>
-              <sz val="10"/>
-            </rPr>
-            <t>（1）两档从「首月特惠 / 月度」改成</t>
-          </r>
-          <r>
-            <rPr>
-              <b val="1"/>
-              <color rgb="00DC2626"/>
-              <sz val="10"/>
-            </rPr>
-            <t>「连续包月」和「单月会员」</t>
-          </r>
-          <r>
-            <rPr>
-              <sz val="10"/>
-            </rPr>
-            <t>——买法本身就说明了续不续费，不用再猜。
+          <t>（1）两档从「首月特惠 / 月度」改成「连续包月」和「单月会员」
 （2）连续包月：首月 ¥9.9（原价 ¥19.9），次月起 ¥19.9/月自动扣款；卡片名字旁边直接挂「自动续费 · 可随时取消」，说明里写「退订后当期仍可用至期满」。
 （3）单月会员：¥19.9 买一个月；卡片上挂「一次性购买 · 不自动续费」，说明里写「到期自动失效不扣款，适合先体验一个月」。
-（4）</t>
-          </r>
-          <r>
-            <rPr>
-              <b val="1"/>
-              <color rgb="00DC2626"/>
-              <sz val="10"/>
-            </rPr>
-            <t>价格一分没变</t>
-          </r>
-          <r>
-            <rPr>
-              <sz val="10"/>
-            </rPr>
-            <t>，变的是把「下个月还扣不扣钱」从小字里提到卡片名字旁边——原来客服咨询最集中的就是这个问题：用户分不清自己买的是一个月还是会一直扣。
-（5）底部按钮文案跟着所选方式变：「¥9.9 开通连续包月」/「¥19.9 购买单月会员」。
-（6）页面信息顺序重排：先讲买到什么（三枚权益速览 chip），再看套餐，最后勾协议。
-（7）原来按钮下方那段重复讲续费规则的说明删掉了——规则已经在卡片里说清楚，不在页底重复。</t>
-          </r>
+（4）底部按钮文案跟着所选方式变：「¥9.9 开通连续包月」/「¥19.9 购买单月会员」。</t>
         </is>
       </c>
       <c r="D8" s="10" t="inlineStr">
@@ -1772,7 +1735,7 @@
       <c r="G8" s="11" t="n"/>
       <c r="H8" s="11" t="n"/>
     </row>
-    <row r="9" ht="145" customHeight="1">
+    <row r="9" ht="117" customHeight="1">
       <c r="A9" s="8" t="inlineStr">
         <is>
           <t>会员与付费</t>
@@ -1803,25 +1766,10 @@
             <rPr>
               <sz val="10"/>
             </rPr>
-            <t>，用户得自己勾了才能开通。
-（2）选「连续包月」时要同意两份：《会员服务协议》和《自动续费协议》；选「单月会员」只有《会员服务协议》。
-（3）没勾就点开通，会被拦住并提示「请先阅读并同意相关协议」，不进收银台。
-（4）没勾时按钮呈置灰视觉，但仍然可以点——靠提示告诉用户为什么不行，而不是让按钮死掉让人困惑。（测试注意：别去断言按钮的 disabled 属性）
-（5）改这条的原因是</t>
-          </r>
-          <r>
-            <rPr>
-              <b val="1"/>
-              <color rgb="00DC2626"/>
-              <sz val="10"/>
-            </rPr>
-            <t>合规</t>
-          </r>
-          <r>
-            <rPr>
-              <sz val="10"/>
-            </rPr>
-            <t>：自动续费类协议默认帮用户勾上，国内基本不被认可；而且登录页一直是默认不勾的，两边标准不一致本身也说不过去。</t>
+            <t>，需用户主动勾选后方可开通。
+（2）连续包月需同意《会员服务协议》《自动续费协议》两份；单月会员仅《会员服务协议》。
+（3）未勾选点开通：拦截并提示「请先阅读并同意相关协议」，不进收银台。
+（4）未勾选时按钮呈置灰视觉，仍可点击（靠提示拦截，非 disabled）。</t>
           </r>
         </is>
       </c>
@@ -1835,7 +1783,7 @@
       <c r="G9" s="11" t="n"/>
       <c r="H9" s="11" t="n"/>
     </row>
-    <row r="10" ht="188.5" customHeight="1">
+    <row r="10" ht="159.5" customHeight="1">
       <c r="A10" s="8" t="inlineStr">
         <is>
           <t>会员与付费</t>
@@ -1848,32 +1796,13 @@
       </c>
       <c r="C10" s="8" t="inlineStr">
         <is>
-          <r>
-            <rPr>
-              <sz val="10"/>
-            </rPr>
-            <t>（1）价格配置从两个输入框改成</t>
-          </r>
-          <r>
-            <rPr>
-              <b val="1"/>
-              <color rgb="00DC2626"/>
-              <sz val="10"/>
-            </rPr>
-            <t>两组三个</t>
-          </r>
-          <r>
-            <rPr>
-              <sz val="10"/>
-            </rPr>
-            <t>——连续包月组有「首月价格」和「次月起价格」，单月组有「单月价格」。
-（2）每组都挂了和前台一样的续费语义标（「自动续费」/「一次性购买 · 不自动续费」），运营一眼能对上前台是哪张卡。
-（3）每个价格下面有一行说明，写清楚这笔钱什么时候扣。
-（4）「续费规则」原来伪装成一个禁用的输入框，现在改成纯文字说明——只读信息不再看起来像能填的表单。
-（5）续费规则和调价须知合并成一个灰色说明块，写明「支持随时退订，到期赠 72 小时会员缓冲使用期」和「已开通自动续费的用户，下一扣费周期按修改后的价格扣款」。
-（6）点「保存」要二次确认，弹窗说明影响范围（新开通按新价、已开通自动续费的下一周期按新价）。
-（7）「回答策略」的切换同样加了二次确认，点当前已选的那项不触发。</t>
-          </r>
+          <t>（1）价格配置改为两组三个字段：连续包月组「首月价格」「次月起价格」，单月组「单月价格」。
+（2）每组挂与前台一致的续费语义标（「自动续费」/「一次性购买 · 不自动续费」）。
+（3）每个价格下方一行说明，写明扣款时机。
+（4）「续费规则」由禁用输入框改为静态文字说明。
+（5）续费规则与调价须知合并为一个灰色说明块：「支持随时退订，到期赠 72 小时会员缓冲使用期」「已开通自动续费的用户，下一扣费周期按修改后的价格扣款」。
+（6）「保存」加二次确认，说明影响范围。
+（7）「回答策略」切换加二次确认，点当前已选项不触发。</t>
         </is>
       </c>
       <c r="D10" s="10" t="inlineStr">
@@ -1917,7 +1846,7 @@
             <rPr>
               <sz val="10"/>
             </rPr>
-            <t>（1）改成</t>
+            <t>（1）改为</t>
           </r>
           <r>
             <rPr>
@@ -1931,10 +1860,9 @@
             <rPr>
               <sz val="10"/>
             </rPr>
-            <t>——用户发起支付后中途关掉页面，不留任何记录。
-（2）因此读者的「我的订单」里不存在「待支付」这个状态，也不需要「去支付」的入口。
-（3）订单状态收敛成三类：已支付、已核销（兑换码）、退款售后。
-（4）这么改是因为「待支付」订单九成九是垃圾数据——用户点开看看就走了。这些单子占着订单号，运营翻列表要一条条跳过，还得专门写定时任务去清理。</t>
+            <t>，中途关闭页面不留任何记录。
+（2）读者端「我的订单」无「待支付」状态，无「去支付」入口。
+（3）订单状态收敛为三类：已支付、已核销（兑换码）、退款售后。</t>
           </r>
         </is>
       </c>
@@ -1967,7 +1895,7 @@
             <rPr>
               <sz val="10"/>
             </rPr>
-            <t>（1）一笔订单可以退多次（部分退款），所以退款记录改成</t>
+            <t>（1）退款记录</t>
           </r>
           <r>
             <rPr>
@@ -1981,11 +1909,11 @@
             <rPr>
               <sz val="10"/>
             </rPr>
-            <t>。
-（2）订单列表的卡片下方会列出每一笔退款：状态、金额、申请日期。
-（3）订单详情页有独立的「退款记录」卡片，每笔展示退款金额、状态、退款单号、申请时间。
-（4）卡片底部固定两句政策说明：全额退款只撤销由这笔订单单独产生的权益；部分退款以及其他独立赠送、兑换得到的权益不受影响。
-（5）兑换码类型的订单不显示退款卡片（金额为 0，本来也退不了）。</t>
+            <t>（一笔订单可多次部分退款）。
+（2）订单列表卡片下方列出每笔退款：状态、金额、申请日期。
+（3）订单详情页新增「退款记录」卡片，每笔展示退款金额、状态、退款单号、申请时间。
+（4）卡片底部固定政策说明：全额退款仅撤销由该订单单独产生的权益；部分退款及其他独立赠送、兑换权益不受影响。
+（5）兑换码类型订单不显示退款卡片。</t>
           </r>
         </is>
       </c>
@@ -2000,7 +1928,7 @@
       <c r="G13" s="16" t="n"/>
       <c r="H13" s="16" t="n"/>
     </row>
-    <row r="14" ht="145" customHeight="1">
+    <row r="14" ht="117" customHeight="1">
       <c r="A14" s="13" t="inlineStr">
         <is>
           <t>订单与退款</t>
@@ -2013,30 +1941,11 @@
       </c>
       <c r="C14" s="13" t="inlineStr">
         <is>
-          <r>
-            <rPr>
-              <sz val="10"/>
-            </rPr>
-            <t>（1）读者端订单页加了第二行筛选——原来只有类型（全部 / 会员 / 永享 / 兑换码），现在加了状态（全部 / 已支付 / 退款售后）。
-（2）退款中、部分退款、全额退款这三种统一归到「退款售后」一档，读者找退款进度不用在几十条里翻。
-（3）切到「兑换码」这个类型时，状态那一行整行隐藏——能展示的兑换码必然是已核销，多一行是噪音。
-（4）机构后台的订单页，三个时间筛选（下单 / 支付 / 兑换时间）从「摆着不能用」改成真的能筛。
-（5）测试注意：</t>
-          </r>
-          <r>
-            <rPr>
-              <b val="1"/>
-              <color rgb="00DC2626"/>
-              <sz val="10"/>
-            </rPr>
-            <t>一旦启用「兑换时间」筛选，没有兑换时间的普通订单会被排除掉</t>
-          </r>
-          <r>
-            <rPr>
-              <sz val="10"/>
-            </rPr>
-            <t>，这是预期行为。</t>
-          </r>
+          <t>（1）读者端订单页新增状态筛选行（全部 / 已支付 / 退款售后），原类型筛选保留。
+（2）退款中、部分退款、全额退款归并为「退款售后」。
+（3）「兑换码」类型下隐藏状态筛选行。
+（4）机构后台订单页三个时间筛选（下单 / 支付 / 兑换时间）改为真实生效。
+（5）启用「兑换时间」筛选时，无兑换时间的订单被排除。</t>
         </is>
       </c>
       <c r="D14" s="15" t="inlineStr">
@@ -2065,7 +1974,7 @@
       <c r="G15" s="17" t="n"/>
       <c r="H15" s="17" t="n"/>
     </row>
-    <row r="16" ht="188.5" customHeight="1">
+    <row r="16" ht="159.5" customHeight="1">
       <c r="A16" s="18" t="inlineStr">
         <is>
           <t>数据看板</t>
@@ -2082,7 +1991,7 @@
             <rPr>
               <sz val="10"/>
             </rPr>
-            <t>（1）留存改成按</t>
+            <t>（1）留存改按</t>
           </r>
           <r>
             <rPr>
@@ -2096,10 +2005,10 @@
             <rPr>
               <sz val="10"/>
             </rPr>
-            <t>算——统计的是「某一天注册的这批人，过了 N 天还回不回来」，而不是跟着页面上的时间筛选变。
-（2）页面上是三张卡：次日留存、7 日留存、30 日留存。
-（3）每张卡用大白话写清楚统计的是谁，比如「统计 7 月 12 日注册的 976 人 · 第 7 天是否回来」。
-（4）还没到统计时间的节点</t>
+            <t>统计：某日注册用户在第 N 天的回访率，不随页面时间筛选变化。
+（2）三张卡：次日留存、7 日留存、30 日留存。
+（3）每张卡标明统计对象，如「统计 7 月 12 日注册的 976 人 · 第 7 天是否回来」。
+（4）未到统计时间的节点</t>
           </r>
           <r>
             <rPr>
@@ -2113,9 +2022,9 @@
             <rPr>
               <sz val="10"/>
             </rPr>
-            <t>（那会被误读成「一个人都没回来」），而是明说「尚未到统计时间」并给出预计哪天能看。
-（5）右上角可以切注册批次：最新可统计 / 近 7 个注册日 / 近 30 个注册日 / 自定义某一天。
-（6）留存这一段和下面「区间分析」的时间筛选</t>
+            <t>，显示「尚未到统计时间」及预计可统计日期。
+（5）注册批次可切换：最新可统计 / 近 7 个注册日 / 近 30 个注册日 / 自定义单日。
+（6）留存段与「区间分析」的时间筛选</t>
           </r>
           <r>
             <rPr>
@@ -2129,8 +2038,8 @@
             <rPr>
               <sz val="10"/>
             </rPr>
-            <t>——切时间筛选留存卡不动，切注册批次下面的数字不动。这是设计，不是联动 bug。
-（7）选自定义某一天时，三个节点用的是同一批人（同一天注册的），所以分母相同。</t>
+            <t>。
+（7）自定义单日批次的三个节点共用同一样本，分母相同。</t>
           </r>
         </is>
       </c>
@@ -2161,7 +2070,7 @@
             <rPr>
               <sz val="10"/>
             </rPr>
-            <t>（1）这三个数字改成</t>
+            <t>（1）三项指标改为</t>
           </r>
           <r>
             <rPr>
@@ -2169,17 +2078,16 @@
               <color rgb="00DC2626"/>
               <sz val="10"/>
             </rPr>
-            <t>跟着页面上的时间筛选联动</t>
-          </r>
-          <r>
-            <rPr>
-              <sz val="10"/>
-            </rPr>
-            <t>，并且给出和上一周期的对比。
-（2）原来是固定窗口的快照，切时间筛选它纹丝不动，提示里还专门写「不随区间变化」——运营每次都要问一遍是不是坏了。
-（3）口径是所选区间内的日均去重活跃用户。
-（4）「新增用户」单独成一张卡，右边配了一条跟着区间变的迷你趋势线。
-（5）「来源分布」（扫码进入 vs 直接访问）的图例补上了具体人数和占比的环比。</t>
+            <t>随时间筛选联动</t>
+          </r>
+          <r>
+            <rPr>
+              <sz val="10"/>
+            </rPr>
+            <t>，并给出与上一周期的环比。
+（2）口径为所选区间内日均去重活跃用户。
+（3）「新增用户」独立成卡，右侧配随区间变化的迷你趋势线。
+（4）「来源分布」图例补充具体人数与占比环比。</t>
           </r>
         </is>
       </c>
@@ -2194,7 +2102,7 @@
       <c r="G17" s="21" t="n"/>
       <c r="H17" s="21" t="n"/>
     </row>
-    <row r="18" ht="130.5" customHeight="1">
+    <row r="18" ht="117" customHeight="1">
       <c r="A18" s="18" t="inlineStr">
         <is>
           <t>数据看板</t>
@@ -2211,8 +2119,8 @@
             <rPr>
               <sz val="10"/>
             </rPr>
-            <t>（1）所有指标的环比后面都跟上了具体的对比时间窗，比如「较上一周期 · 对比 07-06—07-12」，不用猜是跟什么比的。
-（2）上一周期数值为 0 时</t>
+            <t>（1）环比后附具体对比时间窗，如「较上一周期 · 对比 07-06—07-12」。
+（2）上一周期为 0 时</t>
           </r>
           <r>
             <rPr>
@@ -2220,16 +2128,15 @@
               <color rgb="00DC2626"/>
               <sz val="10"/>
             </rPr>
-            <t>不再显示 0%</t>
-          </r>
-          <r>
-            <rPr>
-              <sz val="10"/>
-            </rPr>
-            <t>（会被读成「没变化」），而是明说「上期为 0，暂无可比增幅」。
-（3）率类指标（比如退款率）的变化用百分点表示，计数和金额类用百分比。
-（4）所有指标的问号说明统一由一处生成，三端口径一致，改文案只改一个地方。
-（5）测试注意：环比标签里的日期是按当前系统时间算的，拿截图做基线对比的回归会一直报差异。</t>
+            <t>不显示 0%</t>
+          </r>
+          <r>
+            <rPr>
+              <sz val="10"/>
+            </rPr>
+            <t>，显示「上期为 0，暂无可比增幅」。
+（3）率类指标变化用百分点，计数与金额类用百分比。
+（4）指标说明文案统一由一处生成，三端口径一致。</t>
           </r>
         </is>
       </c>
@@ -2258,7 +2165,7 @@
       <c r="G19" s="22" t="n"/>
       <c r="H19" s="22" t="n"/>
     </row>
-    <row r="20" ht="203" customHeight="1">
+    <row r="20" ht="130.5" customHeight="1">
       <c r="A20" s="23" t="inlineStr">
         <is>
           <t>机构与订阅</t>
@@ -2275,7 +2182,7 @@
             <rPr>
               <sz val="10"/>
             </rPr>
-            <t>（1）机构只允许</t>
+            <t>（1）机构层级限</t>
           </r>
           <r>
             <rPr>
@@ -2289,10 +2196,10 @@
             <rPr>
               <sz val="10"/>
             </rPr>
-            <t>：父机构（出版集团）和子机构（分社），不能再往下套。
-（2）列表里只给父机构挂「父机构」标签，子机构由「上级机构」这一列体现，普通机构不挂标签。这个标签是从关系里自动算出来的，不用人工维护，也就不会出现「标了父机构其实下面没有分社」这种脏数据。
-（3）机构详情页的「上级机构」按三种情况给三种界面：子机构可以改挂到别的集团、也可以解除关联变成独立机构；已经是父机构的那一栏直接禁用（不能再给自己挂上级）；普通机构可以挂到某个顶级机构下。
-（4）改上级和解除关联都要二次确认，弹窗写清楚会发生什么。
+            <t>：父机构与子机构，不支持三层。
+（2）列表仅父机构挂「父机构」标签，标签由机构关系自动推导。
+（3）「上级机构」字段按角色分三种形态：子机构可改挂或解除关联；父机构禁用；普通机构可挂载至顶级机构。
+（4）改挂上级与解除关联均加二次确认。
 （5）</t>
           </r>
           <r>
@@ -2301,15 +2208,15 @@
               <color rgb="00DC2626"/>
               <sz val="10"/>
             </rPr>
-            <t>停用一个父机构，不会连带停用它下面的分社</t>
-          </r>
-          <r>
-            <rPr>
-              <sz val="10"/>
-            </rPr>
-            <t>——分社是独立经营主体，有自己的账和自己的读者，不能因为集团那边欠费就把分社的生意也停了。要停分社得一家家单独确认，停用弹窗里明确写了这一点。
-（6）平台后台各处筛选下拉里，父机构名字后面会带「（父机构）」后缀；选中父机构看用量时，会提示「以下用量已汇总子机构：A、B」。
-（7）新建机构时「机构域名前缀」是必填项，且全平台不能重名。</t>
+            <t>停用父机构不级联停用子机构</t>
+          </r>
+          <r>
+            <rPr>
+              <sz val="10"/>
+            </rPr>
+            <t>，需逐家单独确认，停用弹窗中明确说明。
+（6）平台后台筛选下拉中父机构名带「（父机构）」后缀；选中父机构时提示「以下用量已汇总子机构：A、B」。
+（7）新建机构时「机构域名前缀」必填且全平台唯一。</t>
           </r>
         </is>
       </c>
@@ -2323,7 +2230,7 @@
       <c r="G20" s="26" t="n"/>
       <c r="H20" s="26" t="n"/>
     </row>
-    <row r="21" ht="174" customHeight="1">
+    <row r="21" ht="117" customHeight="1">
       <c r="A21" s="23" t="inlineStr">
         <is>
           <t>机构与订阅</t>
@@ -2340,7 +2247,7 @@
             <rPr>
               <sz val="10"/>
             </rPr>
-            <t>（1）删除条件放宽了：原来要求同时满足四个条件（没过期、三项用量都是 0、没有加油包）才让删，现在</t>
+            <t>（1）删除条件放宽：</t>
           </r>
           <r>
             <rPr>
@@ -2348,16 +2255,16 @@
               <color rgb="00DC2626"/>
               <sz val="10"/>
             </rPr>
-            <t>只有「已过期」的不能删</t>
-          </r>
-          <r>
-            <rPr>
-              <sz val="10"/>
-            </rPr>
-            <t>。
-（2）未生效和已生效的都能删，但确认弹窗会列清楚后果——连带删除这条订阅下的全部加油包、机构立即失去这条订阅的配额。
-（3）如果这条订阅已经产生了用量，弹窗会加一条红色强警告，并写出具体用量数值。
-（4）弹窗底部明确写「</t>
+            <t>仅「已过期」不可删</t>
+          </r>
+          <r>
+            <rPr>
+              <sz val="10"/>
+            </rPr>
+            <t>，未生效与已生效均可删。
+（2）确认弹窗列明后果：连带删除该订阅全部加油包、机构立即失去该订阅配额。
+（3）已产生用量时追加红色强警告，并写出具体用量数值。
+（4）弹窗底部明确「</t>
           </r>
           <r>
             <rPr>
@@ -2371,9 +2278,7 @@
             <rPr>
               <sz val="10"/>
             </rPr>
-            <t>」——删除只是移除记录和配额，不产生退款单，退费走线下商务流程。
-（5）放宽的原因是商务把订阅建错了需要撤销，原来条件卡太死，建错了就永远删不掉、只能挂在那儿看着。
-（6）回归时重点测「删掉正在生效的订阅之后，机构的配额和当前生效订阅卡是什么表现」。</t>
+            <t>」，不产生退款单，退费走线下流程。</t>
           </r>
         </is>
       </c>
@@ -2387,7 +2292,7 @@
       <c r="G21" s="26" t="n"/>
       <c r="H21" s="26" t="n"/>
     </row>
-    <row r="22" ht="203" customHeight="1">
+    <row r="22" ht="145" customHeight="1">
       <c r="A22" s="23" t="inlineStr">
         <is>
           <t>机构与订阅</t>
@@ -2404,7 +2309,7 @@
             <rPr>
               <sz val="10"/>
             </rPr>
-            <t>（1）三项配额现在分两种性质，界面上也标出来了。
+            <t>（1）三项配额分两种计量性质，并在界面标注。
 （2）</t>
           </r>
           <r>
@@ -2413,13 +2318,13 @@
               <color rgb="00DC2626"/>
               <sz val="10"/>
             </rPr>
-            <t>知识产品数和存储是「占用型」</t>
-          </r>
-          <r>
-            <rPr>
-              <sz val="10"/>
-            </rPr>
-            <t>——看的是当前实际占了多少，删掉内容能释放出来，跨订阅周期延续。
+            <t>知识产品数、存储为「占用型」</t>
+          </r>
+          <r>
+            <rPr>
+              <sz val="10"/>
+            </rPr>
+            <t>：按当前实际占用计算，删除内容可释放，跨订阅周期延续。
 （3）</t>
           </r>
           <r>
@@ -2428,17 +2333,16 @@
               <color rgb="00DC2626"/>
               <sz val="10"/>
             </rPr>
-            <t>Token 是「消耗型」</t>
-          </r>
-          <r>
-            <rPr>
-              <sz val="10"/>
-            </rPr>
-            <t>——烧掉就是烧掉，绑定当前订阅周期，换周期归零重新计算，不可回收。
-（4）原来三项都按月累计，导致「删了 KP 配额不释放」和「换订阅周期 Token 不清零」两个说不通的地方。
-（5）额度编辑从空白输入框改成带加减的步进器，选「不限」时禁用（原来能填进去负数和字母）。
-（6）机构用量看板也按这个逻辑拆成两段：上半段是「当前存量」不随时间变，下半段是「区间运营分析」跟着时间筛选走——原来混在一起，运营切时间发现一半动一半不动，以为坏了。
-（7）配额预警短信的口径也跟着改：Token 说的是「本订阅周期消耗已达 X%」。</t>
+            <t>Token 为「消耗型」</t>
+          </r>
+          <r>
+            <rPr>
+              <sz val="10"/>
+            </rPr>
+            <t>：绑定当前订阅周期，换周期归零重计，不可回收。
+（4）额度编辑由输入框改为步进器，选「不限」时禁用。
+（5）机构用量看板拆为两段：「当前存量」不随时间变化，「区间运营分析」随时间筛选联动。
+（6）配额预警短信口径调整：Token 表述为「本订阅周期消耗已达 X%」。</t>
           </r>
         </is>
       </c>
@@ -2467,7 +2371,7 @@
       <c r="G23" s="27" t="n"/>
       <c r="H23" s="27" t="n"/>
     </row>
-    <row r="24" ht="159.5" customHeight="1">
+    <row r="24" ht="117" customHeight="1">
       <c r="A24" s="28" t="inlineStr">
         <is>
           <t>权限与角色</t>
@@ -2484,7 +2388,7 @@
             <rPr>
               <sz val="10"/>
             </rPr>
-            <t>（1）「Agent 回答 Prompt 编辑」不再和其他权限平铺，而是</t>
+            <t>（1）「Agent 回答 Prompt 编辑」由平铺改为</t>
           </r>
           <r>
             <rPr>
@@ -2492,16 +2396,15 @@
               <color rgb="00DC2626"/>
               <sz val="10"/>
             </rPr>
-            <t>缩进挂在「Agent 人设」下面</t>
+            <t>缩进挂在「Agent 人设」下</t>
           </r>
           <r>
             <rPr>
               <sz val="10"/>
             </rPr>
             <t>，用连接线表达从属。
-（2）只有当「Agent 人设」设成「可操作」时，这个子项才会出现；设成「无」或「只读」时它直接不显示。
-（3）原因是：没有保存权限却能编辑 Prompt 是个无意义的组合——编辑完存不了。用层级把这个约束表达出来，管理员配权限时不会配出自相矛盾的组合。
-（4）这个权限点只有两档（只读 / 可操作），</t>
+（2）仅当「Agent 人设 = 可操作」时该子项才渲染，设为「无」或「只读」时不显示。
+（3）该权限点只有两档（只读 / 可操作），</t>
           </r>
           <r>
             <rPr>
@@ -2509,14 +2412,14 @@
               <color rgb="00DC2626"/>
               <sz val="10"/>
             </rPr>
-            <t>没有「无」这一档</t>
-          </r>
-          <r>
-            <rPr>
-              <sz val="10"/>
-            </rPr>
-            <t>，key 行右边挂了「功能权限」小标做区分。
-（5）新建角色时「角色类型」改成锁定态，由从哪个页签进来决定，不能在弹窗里切换（原来「弹窗内切类型」的用例已作废）。</t>
+            <t>无「无」档</t>
+          </r>
+          <r>
+            <rPr>
+              <sz val="10"/>
+            </rPr>
+            <t>，key 行右侧挂「功能权限」标。
+（4）新建角色时「角色类型」为锁定态，由创建入口页签决定，不可在弹窗内切换。</t>
           </r>
         </is>
       </c>
@@ -2544,7 +2447,7 @@
       <c r="G25" s="32" t="n"/>
       <c r="H25" s="32" t="n"/>
     </row>
-    <row r="26" ht="174" customHeight="1">
+    <row r="26" ht="117" customHeight="1">
       <c r="A26" s="33" t="inlineStr">
         <is>
           <t>导出与兑换码</t>
@@ -2561,7 +2464,7 @@
             <rPr>
               <sz val="10"/>
             </rPr>
-            <t>（1）两个后台一共十几个导出按钮，原来大部分点了只弹一句提示、什么都不下载，</t>
+            <t>（1）两个后台的导出按钮全部改为</t>
           </r>
           <r>
             <rPr>
@@ -2569,16 +2472,16 @@
               <color rgb="00DC2626"/>
               <sz val="10"/>
             </rPr>
-            <t>现在都是真的导出 Excel</t>
+            <t>真实导出 Excel</t>
           </r>
           <r>
             <rPr>
               <sz val="10"/>
             </rPr>
             <t>。
-（2）文件名统一规范：机构后台是「AI问书_{机构名}_{业务名}数据导出.xlsx」，平台后台把机构名的位置换成「全域」。
-（3）导出文件的表头区会带上导出时的筛选条件、统计口径和时间范围——拿到文件的人知道这份数据是怎么筛出来的。
-（4）单次导出最多</t>
+（2）文件名规范：机构后台「AI问书_{机构名}_{业务名}数据导出.xlsx」，平台后台机构名位置为「全域」。
+（3）导出文件表头区包含导出时的筛选条件、统计口径与时间范围。
+（4）单次导出上限</t>
           </r>
           <r>
             <rPr>
@@ -2592,9 +2495,8 @@
             <rPr>
               <sz val="10"/>
             </rPr>
-            <t>，超了会弹窗拦住、不下载，提示缩小筛选范围或联系平台管理员。
-（5）测试注意：能触发超限的只有「平台超管 → 全域用户 → 什么筛选都不加 → 导出」这一个入口，别的页面数据量不够。
-（6）文档里的导出模板样张和页面真实导出是同一套逻辑产出的，不会出现「文档说有这列、实际导出没有」。</t>
+            <t>，超限弹窗拦截、不下载，提示缩小筛选范围或联系平台管理员。
+（5）导出模板样张与页面实际导出同源产出。</t>
           </r>
         </is>
       </c>
@@ -2609,7 +2511,7 @@
       <c r="G26" s="36" t="n"/>
       <c r="H26" s="36" t="n"/>
     </row>
-    <row r="27" ht="130.5" customHeight="1">
+    <row r="27" ht="117" customHeight="1">
       <c r="A27" s="33" t="inlineStr">
         <is>
           <t>导出与兑换码</t>
@@ -2634,17 +2536,15 @@
               <color rgb="00DC2626"/>
               <sz val="10"/>
             </rPr>
-            <t>注意这和「权益有效期」是两回事</t>
-          </r>
-          <r>
-            <rPr>
-              <sz val="10"/>
-            </rPr>
-            <t>——前者是这批码什么时候能兑，后者是兑完会员能用多久。
-（2）列表新增这一列、可排序；批次详情抽屉的副标题也会显示。
-（3）读者端兑换失败现在会说清楚原因，分三种：还没到生效时间（并告诉他哪天开始）、已过期、发码机构已停用。
-（4）原来不管输什么都提示「兑换成功」，机构做活动指定某天才能兑的场景完全支持不了。
-（5）上线前记得把读者端那行演示提示（「演示码：FUTURE / EXPIRED / STOPPED」）去掉。</t>
+            <t>与「权益有效期」是两个概念</t>
+          </r>
+          <r>
+            <rPr>
+              <sz val="10"/>
+            </rPr>
+            <t>。
+（2）列表新增该列并可排序，批次详情抽屉副标题同步展示。
+（3）读者端兑换失败区分三种原因：未到生效时间（附生效日期）、已过期、发码机构已停用。</t>
           </r>
         </is>
       </c>

--- a/docs/AI问书-研发同步改动清单.xlsx
+++ b/docs/AI问书-研发同步改动清单.xlsx
@@ -2318,7 +2318,7 @@
               <color rgb="00DC2626"/>
               <sz val="10"/>
             </rPr>
-            <t>知识产品数、存储为「占用型」</t>
+            <t>知识产品数、存储为「占用量」</t>
           </r>
           <r>
             <rPr>
@@ -2333,7 +2333,7 @@
               <color rgb="00DC2626"/>
               <sz val="10"/>
             </rPr>
-            <t>Token 为「消耗型」</t>
+            <t>Token 为「消耗量」</t>
           </r>
           <r>
             <rPr>

--- a/docs/AI问书-研发同步改动清单.xlsx
+++ b/docs/AI问书-研发同步改动清单.xlsx
@@ -17,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="11">
+  <fonts count="12">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -72,8 +72,13 @@
       <color rgb="00BE185D"/>
       <sz val="11"/>
     </font>
+    <font>
+      <b val="1"/>
+      <color rgb="000F766E"/>
+      <sz val="11"/>
+    </font>
   </fonts>
-  <fills count="17">
+  <fills count="19">
     <fill>
       <patternFill/>
     </fill>
@@ -155,6 +160,16 @@
         <fgColor rgb="00FEF4F9"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00D3F3EE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00EFFBF9"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="2">
     <border>
@@ -182,7 +197,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="37">
+  <cellXfs count="42">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -264,6 +279,17 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="16" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="11" fillId="17" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="18" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="18" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="18" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="18" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -571,7 +597,7 @@
     <from>
       <col>4</col>
       <colOff>0</colOff>
-      <row>5</row>
+      <row>6</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="657225" cy="1428750"/>
@@ -596,7 +622,7 @@
     <from>
       <col>5</col>
       <colOff>0</colOff>
-      <row>5</row>
+      <row>6</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="657225" cy="1428750"/>
@@ -621,7 +647,7 @@
     <from>
       <col>4</col>
       <colOff>0</colOff>
-      <row>7</row>
+      <row>8</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="657225" cy="1428750"/>
@@ -646,7 +672,7 @@
     <from>
       <col>4</col>
       <colOff>0</colOff>
-      <row>8</row>
+      <row>9</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="657225" cy="1428750"/>
@@ -671,7 +697,7 @@
     <from>
       <col>5</col>
       <colOff>0</colOff>
-      <row>8</row>
+      <row>9</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="657225" cy="1428750"/>
@@ -696,7 +722,7 @@
     <from>
       <col>4</col>
       <colOff>0</colOff>
-      <row>9</row>
+      <row>10</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="2276475" cy="1428750"/>
@@ -721,7 +747,7 @@
     <from>
       <col>4</col>
       <colOff>0</colOff>
-      <row>11</row>
+      <row>12</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="657225" cy="1428750"/>
@@ -744,19 +770,44 @@
   </oneCellAnchor>
   <oneCellAnchor>
     <from>
+      <col>5</col>
+      <colOff>0</colOff>
+      <row>12</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="657225" cy="1428750"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="17" name="Image 17" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId17"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
       <col>4</col>
       <colOff>0</colOff>
-      <row>12</row>
+      <row>13</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="657225" cy="1428750"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="17" name="Image 17" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId17"/>
+        <cNvPr id="18" name="Image 18" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId18"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -771,17 +822,17 @@
     <from>
       <col>4</col>
       <colOff>0</colOff>
-      <row>13</row>
+      <row>14</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="657225" cy="1428750"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="18" name="Image 18" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId18"/>
+        <cNvPr id="19" name="Image 19" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId19"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -796,17 +847,17 @@
     <from>
       <col>5</col>
       <colOff>0</colOff>
-      <row>13</row>
+      <row>14</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="2276475" cy="1428750"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="19" name="Image 19" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId19"/>
+        <cNvPr id="20" name="Image 20" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId20"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -821,17 +872,17 @@
     <from>
       <col>4</col>
       <colOff>0</colOff>
-      <row>15</row>
+      <row>16</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="2276475" cy="1428750"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="20" name="Image 20" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId20"/>
+        <cNvPr id="21" name="Image 21" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId21"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -846,17 +897,17 @@
     <from>
       <col>4</col>
       <colOff>0</colOff>
-      <row>16</row>
+      <row>17</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="2276475" cy="1428750"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="21" name="Image 21" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId21"/>
+        <cNvPr id="22" name="Image 22" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId22"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -871,17 +922,17 @@
     <from>
       <col>4</col>
       <colOff>0</colOff>
-      <row>17</row>
+      <row>18</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="2276475" cy="1428750"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="22" name="Image 22" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId22"/>
+        <cNvPr id="23" name="Image 23" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId23"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -896,17 +947,17 @@
     <from>
       <col>4</col>
       <colOff>0</colOff>
-      <row>19</row>
+      <row>22</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="2276475" cy="1428750"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="23" name="Image 23" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId23"/>
+        <cNvPr id="24" name="Image 24" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId24"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -921,17 +972,17 @@
     <from>
       <col>5</col>
       <colOff>0</colOff>
-      <row>19</row>
+      <row>22</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="2276475" cy="1428750"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="24" name="Image 24" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId24"/>
+        <cNvPr id="25" name="Image 25" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId25"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -946,17 +997,17 @@
     <from>
       <col>4</col>
       <colOff>0</colOff>
-      <row>20</row>
+      <row>23</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="2276475" cy="1428750"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="25" name="Image 25" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId25"/>
+        <cNvPr id="26" name="Image 26" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId26"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -971,17 +1022,17 @@
     <from>
       <col>4</col>
       <colOff>0</colOff>
-      <row>21</row>
+      <row>24</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="2276475" cy="1428750"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="26" name="Image 26" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId26"/>
+        <cNvPr id="27" name="Image 27" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId27"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -996,17 +1047,67 @@
     <from>
       <col>4</col>
       <colOff>0</colOff>
-      <row>23</row>
+      <row>25</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="4686300" cy="1428750"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="28" name="Image 28" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId28"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>4</col>
+      <colOff>0</colOff>
+      <row>26</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="2352675" cy="1428750"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="29" name="Image 29" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId29"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>4</col>
+      <colOff>0</colOff>
+      <row>28</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="2276475" cy="1428750"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="27" name="Image 27" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId27"/>
+        <cNvPr id="30" name="Image 30" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId30"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -1021,17 +1122,17 @@
     <from>
       <col>4</col>
       <colOff>0</colOff>
-      <row>25</row>
+      <row>30</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="2276475" cy="1428750"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="28" name="Image 28" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId28"/>
+        <cNvPr id="31" name="Image 31" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId31"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -1046,17 +1147,17 @@
     <from>
       <col>4</col>
       <colOff>0</colOff>
-      <row>26</row>
+      <row>31</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="2276475" cy="1428750"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="29" name="Image 29" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId29"/>
+        <cNvPr id="32" name="Image 32" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId32"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -1071,17 +1172,42 @@
     <from>
       <col>5</col>
       <colOff>0</colOff>
-      <row>26</row>
+      <row>31</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="657225" cy="1428750"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="30" name="Image 30" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId30"/>
+        <cNvPr id="33" name="Image 33" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId33"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>4</col>
+      <colOff>0</colOff>
+      <row>33</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="657225" cy="1428750"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="34" name="Image 34" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId34"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -1384,7 +1510,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H27"/>
+  <dimension ref="A1:H34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1639,7 +1765,7 @@
       <c r="G5" s="6" t="n"/>
       <c r="H5" s="6" t="n"/>
     </row>
-    <row r="6" ht="145" customHeight="1">
+    <row r="6" ht="117" customHeight="1">
       <c r="A6" s="3" t="inlineStr">
         <is>
           <t>知识产品 KP</t>
@@ -1647,10 +1773,56 @@
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
+          <t>分享标识只挂在接收方</t>
+        </is>
+      </c>
+      <c r="C6" s="3" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">（1）机构后台知识 KP 列表，分享方 KP </t>
+          </r>
+          <r>
+            <rPr>
+              <b val="1"/>
+              <color rgb="00DC2626"/>
+              <sz val="10"/>
+            </rPr>
+            <t>不再显示「实时分享 · 分享方」标签</t>
+          </r>
+          <r>
+            <rPr>
+              <sz val="10"/>
+            </rPr>
+            <t>，与自建 KP 展示一致。
+（2）分享标识仅保留在接收方：「分享导入 · 实时」「分享导入 · 快照」。</t>
+          </r>
+        </is>
+      </c>
+      <c r="D6" s="5" t="inlineStr">
+        <is>
+          <t>（1）机构后台</t>
+        </is>
+      </c>
+      <c r="E6" s="6" t="n"/>
+      <c r="F6" s="6" t="n"/>
+      <c r="G6" s="6" t="n"/>
+      <c r="H6" s="6" t="n"/>
+    </row>
+    <row r="7" ht="145" customHeight="1">
+      <c r="A7" s="3" t="inlineStr">
+        <is>
+          <t>知识产品 KP</t>
+        </is>
+      </c>
+      <c r="B7" s="4" t="inlineStr">
+        <is>
           <t>读者扫码 / 点链接进来怎么判活</t>
         </is>
       </c>
-      <c r="C6" s="3" t="inlineStr">
+      <c r="C7" s="3" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -1681,43 +1853,43 @@
           </r>
         </is>
       </c>
-      <c r="D6" s="5" t="inlineStr">
+      <c r="D7" s="5" t="inlineStr">
         <is>
           <t>（1）移动端
 （2）机构后台</t>
         </is>
       </c>
-      <c r="E6" s="6" t="n"/>
-      <c r="F6" s="6" t="n"/>
-      <c r="G6" s="6" t="n"/>
-      <c r="H6" s="6" t="n"/>
-    </row>
-    <row r="7" ht="22" customHeight="1">
-      <c r="A7" s="7" t="inlineStr">
+      <c r="E7" s="6" t="n"/>
+      <c r="F7" s="6" t="n"/>
+      <c r="G7" s="6" t="n"/>
+      <c r="H7" s="6" t="n"/>
+    </row>
+    <row r="8" ht="22" customHeight="1">
+      <c r="A8" s="7" t="inlineStr">
         <is>
           <t>■ 会员与付费</t>
         </is>
       </c>
-      <c r="B7" s="7" t="n"/>
-      <c r="C7" s="7" t="n"/>
-      <c r="D7" s="7" t="n"/>
-      <c r="E7" s="7" t="n"/>
-      <c r="F7" s="7" t="n"/>
-      <c r="G7" s="7" t="n"/>
-      <c r="H7" s="7" t="n"/>
-    </row>
-    <row r="8" ht="117" customHeight="1">
-      <c r="A8" s="8" t="inlineStr">
+      <c r="B8" s="7" t="n"/>
+      <c r="C8" s="7" t="n"/>
+      <c r="D8" s="7" t="n"/>
+      <c r="E8" s="7" t="n"/>
+      <c r="F8" s="7" t="n"/>
+      <c r="G8" s="7" t="n"/>
+      <c r="H8" s="7" t="n"/>
+    </row>
+    <row r="9" ht="117" customHeight="1">
+      <c r="A9" s="8" t="inlineStr">
         <is>
           <t>会员与付费</t>
         </is>
       </c>
-      <c r="B8" s="9" t="inlineStr">
+      <c r="B9" s="9" t="inlineStr">
         <is>
           <t>两种购买方式与自动续费规则</t>
         </is>
       </c>
-      <c r="C8" s="8" t="inlineStr">
+      <c r="C9" s="8" t="inlineStr">
         <is>
           <t>（1）两档从「首月特惠 / 月度」改成「连续包月」和「单月会员」
 （2）连续包月：首月 ¥9.9（原价 ¥19.9），次月起 ¥19.9/月自动扣款；卡片名字旁边直接挂「自动续费 · 可随时取消」，说明里写「退订后当期仍可用至期满」。
@@ -1725,28 +1897,28 @@
 （4）底部按钮文案跟着所选方式变：「¥9.9 开通连续包月」/「¥19.9 购买单月会员」。</t>
         </is>
       </c>
-      <c r="D8" s="10" t="inlineStr">
+      <c r="D9" s="10" t="inlineStr">
         <is>
           <t>（1）移动端</t>
         </is>
       </c>
-      <c r="E8" s="11" t="n"/>
-      <c r="F8" s="11" t="n"/>
-      <c r="G8" s="11" t="n"/>
-      <c r="H8" s="11" t="n"/>
-    </row>
-    <row r="9" ht="117" customHeight="1">
-      <c r="A9" s="8" t="inlineStr">
+      <c r="E9" s="11" t="n"/>
+      <c r="F9" s="11" t="n"/>
+      <c r="G9" s="11" t="n"/>
+      <c r="H9" s="11" t="n"/>
+    </row>
+    <row r="10" ht="117" customHeight="1">
+      <c r="A10" s="8" t="inlineStr">
         <is>
           <t>会员与付费</t>
         </is>
       </c>
-      <c r="B9" s="9" t="inlineStr">
+      <c r="B10" s="9" t="inlineStr">
         <is>
           <t>开通页的协议勾选</t>
         </is>
       </c>
-      <c r="C9" s="8" t="inlineStr">
+      <c r="C10" s="8" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -1773,28 +1945,28 @@
           </r>
         </is>
       </c>
-      <c r="D9" s="10" t="inlineStr">
+      <c r="D10" s="10" t="inlineStr">
         <is>
           <t>（1）移动端</t>
         </is>
       </c>
-      <c r="E9" s="11" t="n"/>
-      <c r="F9" s="11" t="n"/>
-      <c r="G9" s="11" t="n"/>
-      <c r="H9" s="11" t="n"/>
-    </row>
-    <row r="10" ht="159.5" customHeight="1">
-      <c r="A10" s="8" t="inlineStr">
+      <c r="E10" s="11" t="n"/>
+      <c r="F10" s="11" t="n"/>
+      <c r="G10" s="11" t="n"/>
+      <c r="H10" s="11" t="n"/>
+    </row>
+    <row r="11" ht="159.5" customHeight="1">
+      <c r="A11" s="8" t="inlineStr">
         <is>
           <t>会员与付费</t>
         </is>
       </c>
-      <c r="B10" s="9" t="inlineStr">
+      <c r="B11" s="9" t="inlineStr">
         <is>
           <t>后台的会员价格配置</t>
         </is>
       </c>
-      <c r="C10" s="8" t="inlineStr">
+      <c r="C11" s="8" t="inlineStr">
         <is>
           <t>（1）价格配置改为两组三个字段：连续包月组「首月价格」「次月起价格」，单月组「单月价格」。
 （2）每组挂与前台一致的续费语义标（「自动续费」/「一次性购买 · 不自动续费」）。
@@ -1805,91 +1977,137 @@
 （7）「回答策略」切换加二次确认，点当前已选项不触发。</t>
         </is>
       </c>
-      <c r="D10" s="10" t="inlineStr">
+      <c r="D11" s="10" t="inlineStr">
         <is>
           <t>（1）机构后台</t>
         </is>
       </c>
-      <c r="E10" s="11" t="n"/>
-      <c r="F10" s="11" t="n"/>
-      <c r="G10" s="11" t="n"/>
-      <c r="H10" s="11" t="n"/>
-    </row>
-    <row r="11" ht="22" customHeight="1">
-      <c r="A11" s="12" t="inlineStr">
+      <c r="E11" s="11" t="n"/>
+      <c r="F11" s="11" t="n"/>
+      <c r="G11" s="11" t="n"/>
+      <c r="H11" s="11" t="n"/>
+    </row>
+    <row r="12" ht="22" customHeight="1">
+      <c r="A12" s="12" t="inlineStr">
         <is>
           <t>■ 订单与退款</t>
         </is>
       </c>
-      <c r="B11" s="12" t="n"/>
-      <c r="C11" s="12" t="n"/>
-      <c r="D11" s="12" t="n"/>
-      <c r="E11" s="12" t="n"/>
-      <c r="F11" s="12" t="n"/>
-      <c r="G11" s="12" t="n"/>
-      <c r="H11" s="12" t="n"/>
-    </row>
-    <row r="12" ht="117" customHeight="1">
-      <c r="A12" s="13" t="inlineStr">
+      <c r="B12" s="12" t="n"/>
+      <c r="C12" s="12" t="n"/>
+      <c r="D12" s="12" t="n"/>
+      <c r="E12" s="12" t="n"/>
+      <c r="F12" s="12" t="n"/>
+      <c r="G12" s="12" t="n"/>
+      <c r="H12" s="12" t="n"/>
+    </row>
+    <row r="13" ht="217.5" customHeight="1">
+      <c r="A13" s="13" t="inlineStr">
         <is>
           <t>订单与退款</t>
         </is>
       </c>
-      <c r="B12" s="14" t="inlineStr">
-        <is>
-          <t>订单什么时候生成</t>
-        </is>
-      </c>
-      <c r="C12" s="13" t="inlineStr">
-        <is>
-          <r>
-            <rPr>
-              <sz val="10"/>
-            </rPr>
-            <t>（1）改为</t>
-          </r>
-          <r>
-            <rPr>
-              <b val="1"/>
-              <color rgb="00DC2626"/>
-              <sz val="10"/>
-            </rPr>
-            <t>支付成功才生成订单</t>
-          </r>
-          <r>
-            <rPr>
-              <sz val="10"/>
-            </rPr>
-            <t>，中途关闭页面不留任何记录。
-（2）读者端「我的订单」无「待支付」状态，无「去支付」入口。
-（3）订单状态收敛为三类：已支付、已核销（兑换码）、退款售后。</t>
-          </r>
-        </is>
-      </c>
-      <c r="D12" s="15" t="inlineStr">
+      <c r="B13" s="14" t="inlineStr">
+        <is>
+          <t>订单状态四态与什么时候落库</t>
+        </is>
+      </c>
+      <c r="C13" s="13" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="10"/>
+            </rPr>
+            <t>（1）</t>
+          </r>
+          <r>
+            <rPr>
+              <b val="1"/>
+              <color rgb="00DC2626"/>
+              <sz val="10"/>
+            </rPr>
+            <t>发起支付即落库</t>
+          </r>
+          <r>
+            <rPr>
+              <sz val="10"/>
+            </rPr>
+            <t>创建订单，30 分钟支付有效期，下单时传 time_expire、到期微信自动关单。
+（2）订单状态收敛为四态：</t>
+          </r>
+          <r>
+            <rPr>
+              <b val="1"/>
+              <color rgb="00DC2626"/>
+              <sz val="10"/>
+            </rPr>
+            <t>待支付 / 已支付 / 已核销（兑换码）/ 已失效</t>
+          </r>
+          <r>
+            <rPr>
+              <sz val="10"/>
+            </rPr>
+            <t>；退款/售后为独立维度，不占用订单状态位。
+（3）网页支付无「支付失败」态：支付失败的订单停留在「待支付」，可换支付方式重试。
+（4）C 端「我的订单」状态筛选改五档：全部 / 待支付 / 已支付 / 已失效 / 退款售后；待支付订单显示剩余支付时间倒计时 + 「去支付」按钮。
+（5）兑换码核销单归入「已支付」组，行内标签仍显示「已核销」。
+（6）两后台订单状态筛选为：全部 / 待支付 / 已支付 / 已核销 / 已失效；</t>
+          </r>
+          <r>
+            <rPr>
+              <b val="1"/>
+              <color rgb="00DC2626"/>
+              <sz val="10"/>
+            </rPr>
+            <t>仅「已支付」订单可发起退款</t>
+          </r>
+          <r>
+            <rPr>
+              <sz val="10"/>
+            </rPr>
+            <t>；待支付、已失效订单付款时间显示「—」。
+（7）GMV、付费用户等营收指标</t>
+          </r>
+          <r>
+            <rPr>
+              <b val="1"/>
+              <color rgb="00DC2626"/>
+              <sz val="10"/>
+            </rPr>
+            <t>仅计入「已支付」订单</t>
+          </r>
+          <r>
+            <rPr>
+              <sz val="10"/>
+            </rPr>
+            <t>，待支付、已失效不计入，相关指标 tooltip 注明。</t>
+          </r>
+        </is>
+      </c>
+      <c r="D13" s="15" t="inlineStr">
         <is>
           <t>（1）移动端
 （2）机构后台
 （3）平台超管</t>
         </is>
       </c>
-      <c r="E12" s="16" t="n"/>
-      <c r="F12" s="16" t="n"/>
-      <c r="G12" s="16" t="n"/>
-      <c r="H12" s="16" t="n"/>
-    </row>
-    <row r="13" ht="117" customHeight="1">
-      <c r="A13" s="13" t="inlineStr">
+      <c r="E13" s="16" t="n"/>
+      <c r="F13" s="16" t="n"/>
+      <c r="G13" s="16" t="n"/>
+      <c r="H13" s="16" t="n"/>
+    </row>
+    <row r="14" ht="117" customHeight="1">
+      <c r="A14" s="13" t="inlineStr">
         <is>
           <t>订单与退款</t>
         </is>
       </c>
-      <c r="B13" s="14" t="inlineStr">
+      <c r="B14" s="14" t="inlineStr">
         <is>
           <t>退款记录怎么展示</t>
         </is>
       </c>
-      <c r="C13" s="13" t="inlineStr">
+      <c r="C14" s="13" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -1917,75 +2135,75 @@
           </r>
         </is>
       </c>
-      <c r="D13" s="15" t="inlineStr">
+      <c r="D14" s="15" t="inlineStr">
         <is>
           <t>（1）移动端
 （2）机构后台</t>
         </is>
       </c>
-      <c r="E13" s="16" t="n"/>
-      <c r="F13" s="16" t="n"/>
-      <c r="G13" s="16" t="n"/>
-      <c r="H13" s="16" t="n"/>
-    </row>
-    <row r="14" ht="117" customHeight="1">
-      <c r="A14" s="13" t="inlineStr">
+      <c r="E14" s="16" t="n"/>
+      <c r="F14" s="16" t="n"/>
+      <c r="G14" s="16" t="n"/>
+      <c r="H14" s="16" t="n"/>
+    </row>
+    <row r="15" ht="117" customHeight="1">
+      <c r="A15" s="13" t="inlineStr">
         <is>
           <t>订单与退款</t>
         </is>
       </c>
-      <c r="B14" s="14" t="inlineStr">
+      <c r="B15" s="14" t="inlineStr">
         <is>
           <t>订单怎么筛</t>
         </is>
       </c>
-      <c r="C14" s="13" t="inlineStr">
-        <is>
-          <t>（1）读者端订单页新增状态筛选行（全部 / 已支付 / 退款售后），原类型筛选保留。
+      <c r="C15" s="13" t="inlineStr">
+        <is>
+          <t>（1）读者端订单页新增状态筛选行（五档见上一条），原类型筛选保留，双维度过滤。
 （2）退款中、部分退款、全额退款归并为「退款售后」。
 （3）「兑换码」类型下隐藏状态筛选行。
 （4）机构后台订单页三个时间筛选（下单 / 支付 / 兑换时间）改为真实生效。
 （5）启用「兑换时间」筛选时，无兑换时间的订单被排除。</t>
         </is>
       </c>
-      <c r="D14" s="15" t="inlineStr">
+      <c r="D15" s="15" t="inlineStr">
         <is>
           <t>（1）移动端
 （2）机构后台
 （3）平台超管</t>
         </is>
       </c>
-      <c r="E14" s="16" t="n"/>
-      <c r="F14" s="16" t="n"/>
-      <c r="G14" s="16" t="n"/>
-      <c r="H14" s="16" t="n"/>
-    </row>
-    <row r="15" ht="22" customHeight="1">
-      <c r="A15" s="17" t="inlineStr">
+      <c r="E15" s="16" t="n"/>
+      <c r="F15" s="16" t="n"/>
+      <c r="G15" s="16" t="n"/>
+      <c r="H15" s="16" t="n"/>
+    </row>
+    <row r="16" ht="22" customHeight="1">
+      <c r="A16" s="17" t="inlineStr">
         <is>
           <t>■ 数据看板</t>
         </is>
       </c>
-      <c r="B15" s="17" t="n"/>
-      <c r="C15" s="17" t="n"/>
-      <c r="D15" s="17" t="n"/>
-      <c r="E15" s="17" t="n"/>
-      <c r="F15" s="17" t="n"/>
-      <c r="G15" s="17" t="n"/>
-      <c r="H15" s="17" t="n"/>
-    </row>
-    <row r="16" ht="159.5" customHeight="1">
-      <c r="A16" s="18" t="inlineStr">
+      <c r="B16" s="17" t="n"/>
+      <c r="C16" s="17" t="n"/>
+      <c r="D16" s="17" t="n"/>
+      <c r="E16" s="17" t="n"/>
+      <c r="F16" s="17" t="n"/>
+      <c r="G16" s="17" t="n"/>
+      <c r="H16" s="17" t="n"/>
+    </row>
+    <row r="17" ht="159.5" customHeight="1">
+      <c r="A17" s="18" t="inlineStr">
         <is>
           <t>数据看板</t>
         </is>
       </c>
-      <c r="B16" s="19" t="inlineStr">
+      <c r="B17" s="19" t="inlineStr">
         <is>
           <t>用户留存怎么算</t>
         </is>
       </c>
-      <c r="C16" s="18" t="inlineStr">
+      <c r="C17" s="18" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -2043,28 +2261,28 @@
           </r>
         </is>
       </c>
-      <c r="D16" s="20" t="inlineStr">
+      <c r="D17" s="20" t="inlineStr">
         <is>
           <t>（1）机构后台</t>
         </is>
       </c>
-      <c r="E16" s="21" t="n"/>
-      <c r="F16" s="21" t="n"/>
-      <c r="G16" s="21" t="n"/>
-      <c r="H16" s="21" t="n"/>
-    </row>
-    <row r="17" ht="117" customHeight="1">
-      <c r="A17" s="18" t="inlineStr">
+      <c r="E17" s="21" t="n"/>
+      <c r="F17" s="21" t="n"/>
+      <c r="G17" s="21" t="n"/>
+      <c r="H17" s="21" t="n"/>
+    </row>
+    <row r="18" ht="117" customHeight="1">
+      <c r="A18" s="18" t="inlineStr">
         <is>
           <t>数据看板</t>
         </is>
       </c>
-      <c r="B17" s="19" t="inlineStr">
+      <c r="B18" s="19" t="inlineStr">
         <is>
           <t>日活 / 周活 / 月活的口径</t>
         </is>
       </c>
-      <c r="C17" s="18" t="inlineStr">
+      <c r="C18" s="18" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -2091,55 +2309,6 @@
           </r>
         </is>
       </c>
-      <c r="D17" s="20" t="inlineStr">
-        <is>
-          <t>（1）机构后台
-（2）平台超管</t>
-        </is>
-      </c>
-      <c r="E17" s="21" t="n"/>
-      <c r="F17" s="21" t="n"/>
-      <c r="G17" s="21" t="n"/>
-      <c r="H17" s="21" t="n"/>
-    </row>
-    <row r="18" ht="117" customHeight="1">
-      <c r="A18" s="18" t="inlineStr">
-        <is>
-          <t>数据看板</t>
-        </is>
-      </c>
-      <c r="B18" s="19" t="inlineStr">
-        <is>
-          <t>指标环比怎么显示</t>
-        </is>
-      </c>
-      <c r="C18" s="18" t="inlineStr">
-        <is>
-          <r>
-            <rPr>
-              <sz val="10"/>
-            </rPr>
-            <t>（1）环比后附具体对比时间窗，如「较上一周期 · 对比 07-06—07-12」。
-（2）上一周期为 0 时</t>
-          </r>
-          <r>
-            <rPr>
-              <b val="1"/>
-              <color rgb="00DC2626"/>
-              <sz val="10"/>
-            </rPr>
-            <t>不显示 0%</t>
-          </r>
-          <r>
-            <rPr>
-              <sz val="10"/>
-            </rPr>
-            <t>，显示「上期为 0，暂无可比增幅」。
-（3）率类指标变化用百分点，计数与金额类用百分比。
-（4）指标说明文案统一由一处生成，三端口径一致。</t>
-          </r>
-        </is>
-      </c>
       <c r="D18" s="20" t="inlineStr">
         <is>
           <t>（1）机构后台
@@ -2151,32 +2320,221 @@
       <c r="G18" s="21" t="n"/>
       <c r="H18" s="21" t="n"/>
     </row>
-    <row r="19" ht="22" customHeight="1">
-      <c r="A19" s="22" t="inlineStr">
+    <row r="19" ht="117" customHeight="1">
+      <c r="A19" s="18" t="inlineStr">
+        <is>
+          <t>数据看板</t>
+        </is>
+      </c>
+      <c r="B19" s="19" t="inlineStr">
+        <is>
+          <t>指标环比怎么显示</t>
+        </is>
+      </c>
+      <c r="C19" s="18" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="10"/>
+            </rPr>
+            <t>（1）环比后附具体对比时间窗，如「较上一周期 · 对比 07-06—07-12」。
+（2）上一周期为 0 时</t>
+          </r>
+          <r>
+            <rPr>
+              <b val="1"/>
+              <color rgb="00DC2626"/>
+              <sz val="10"/>
+            </rPr>
+            <t>不显示 0%</t>
+          </r>
+          <r>
+            <rPr>
+              <sz val="10"/>
+            </rPr>
+            <t>，显示「上期为 0，暂无可比增幅」。
+（3）率类指标变化用百分点，计数与金额类用百分比。
+（4）指标说明文案统一由一处生成，三端口径一致。</t>
+          </r>
+        </is>
+      </c>
+      <c r="D19" s="20" t="inlineStr">
+        <is>
+          <t>（1）机构后台
+（2）平台超管</t>
+        </is>
+      </c>
+      <c r="E19" s="21" t="n"/>
+      <c r="F19" s="21" t="n"/>
+      <c r="G19" s="21" t="n"/>
+      <c r="H19" s="21" t="n"/>
+    </row>
+    <row r="20" ht="117" customHeight="1">
+      <c r="A20" s="18" t="inlineStr">
+        <is>
+          <t>数据看板</t>
+        </is>
+      </c>
+      <c r="B20" s="19" t="inlineStr">
+        <is>
+          <t>会员指标分新增 / 续费 / 回流</t>
+        </is>
+      </c>
+      <c r="C20" s="18" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="10"/>
+            </rPr>
+            <t>（1）「新增会员」口径修订为区间内</t>
+          </r>
+          <r>
+            <rPr>
+              <b val="1"/>
+              <color rgb="00DC2626"/>
+              <sz val="10"/>
+            </rPr>
+            <t>历史首次</t>
+          </r>
+          <r>
+            <rPr>
+              <sz val="10"/>
+            </rPr>
+            <t>开通会员的用户数，续费、回流均不计入。
+（2）续费率 = 区间内到期且完成续费的会员数 ÷ 同区间到期会员数；机构后台已有，</t>
+          </r>
+          <r>
+            <rPr>
+              <b val="1"/>
+              <color rgb="00DC2626"/>
+              <sz val="10"/>
+            </rPr>
+            <t>平台后台本批新增</t>
+          </r>
+          <r>
+            <rPr>
+              <sz val="10"/>
+            </rPr>
+            <t>。
+（3）「回流会员」两后台新增：区间内开通会员、且开通时会员状态为已过期的用户数。
+（4）</t>
+          </r>
+          <r>
+            <rPr>
+              <b val="1"/>
+              <color rgb="00DC2626"/>
+              <sz val="10"/>
+            </rPr>
+            <t>三者互斥</t>
+          </r>
+          <r>
+            <rPr>
+              <sz val="10"/>
+            </rPr>
+            <t>：任一次开通行为只落入其中一类。
+（5）两后台主控台与数据看板的会员 KPI 行改为 3 列。</t>
+          </r>
+        </is>
+      </c>
+      <c r="D20" s="20" t="inlineStr">
+        <is>
+          <t>（1）机构后台
+（2）平台超管</t>
+        </is>
+      </c>
+      <c r="E20" s="21" t="n"/>
+      <c r="F20" s="21" t="n"/>
+      <c r="G20" s="21" t="n"/>
+      <c r="H20" s="21" t="n"/>
+    </row>
+    <row r="21" ht="117" customHeight="1">
+      <c r="A21" s="18" t="inlineStr">
+        <is>
+          <t>数据看板</t>
+        </is>
+      </c>
+      <c r="B21" s="19" t="inlineStr">
+        <is>
+          <t>指标去重规则全量标注</t>
+        </is>
+      </c>
+      <c r="C21" s="18" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="10"/>
+            </rPr>
+            <t>（1）</t>
+          </r>
+          <r>
+            <rPr>
+              <b val="1"/>
+              <color rgb="00DC2626"/>
+              <sz val="10"/>
+            </rPr>
+            <t>规模指标按用户去重</t>
+          </r>
+          <r>
+            <rPr>
+              <sz val="10"/>
+            </rPr>
+            <t>：区间内按用户 ID 精确去重，同一用户多天活跃只算 1 人；适用活跃用户、新增 C 端、付费用户、提问用户等。
+（2）</t>
+          </r>
+          <r>
+            <rPr>
+              <b val="1"/>
+              <color rgb="00DC2626"/>
+              <sz val="10"/>
+            </rPr>
+            <t>强度指标按人天</t>
+          </r>
+          <r>
+            <rPr>
+              <sz val="10"/>
+            </rPr>
+            <t>：按用户 × 自然日累计；适用日均活跃、人均提问等。
+（3）两后台所有涉及去重的指标 tooltip 标注所属类别与去重口径，导出的口径说明同步。</t>
+          </r>
+        </is>
+      </c>
+      <c r="D21" s="20" t="inlineStr">
+        <is>
+          <t>（1）机构后台
+（2）平台超管</t>
+        </is>
+      </c>
+      <c r="E21" s="21" t="n"/>
+      <c r="F21" s="21" t="n"/>
+      <c r="G21" s="21" t="n"/>
+      <c r="H21" s="21" t="n"/>
+    </row>
+    <row r="22" ht="22" customHeight="1">
+      <c r="A22" s="22" t="inlineStr">
         <is>
           <t>■ 机构与订阅</t>
         </is>
       </c>
-      <c r="B19" s="22" t="n"/>
-      <c r="C19" s="22" t="n"/>
-      <c r="D19" s="22" t="n"/>
-      <c r="E19" s="22" t="n"/>
-      <c r="F19" s="22" t="n"/>
-      <c r="G19" s="22" t="n"/>
-      <c r="H19" s="22" t="n"/>
-    </row>
-    <row r="20" ht="130.5" customHeight="1">
-      <c r="A20" s="23" t="inlineStr">
+      <c r="B22" s="22" t="n"/>
+      <c r="C22" s="22" t="n"/>
+      <c r="D22" s="22" t="n"/>
+      <c r="E22" s="22" t="n"/>
+      <c r="F22" s="22" t="n"/>
+      <c r="G22" s="22" t="n"/>
+      <c r="H22" s="22" t="n"/>
+    </row>
+    <row r="23" ht="130.5" customHeight="1">
+      <c r="A23" s="23" t="inlineStr">
         <is>
           <t>机构与订阅</t>
         </is>
       </c>
-      <c r="B20" s="24" t="inlineStr">
+      <c r="B23" s="24" t="inlineStr">
         <is>
           <t>父机构 / 子机构怎么管</t>
         </is>
       </c>
-      <c r="C20" s="23" t="inlineStr">
+      <c r="C23" s="23" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -2220,28 +2578,28 @@
           </r>
         </is>
       </c>
-      <c r="D20" s="25" t="inlineStr">
+      <c r="D23" s="25" t="inlineStr">
         <is>
           <t>（1）平台超管</t>
         </is>
       </c>
-      <c r="E20" s="26" t="n"/>
-      <c r="F20" s="26" t="n"/>
-      <c r="G20" s="26" t="n"/>
-      <c r="H20" s="26" t="n"/>
-    </row>
-    <row r="21" ht="117" customHeight="1">
-      <c r="A21" s="23" t="inlineStr">
+      <c r="E23" s="26" t="n"/>
+      <c r="F23" s="26" t="n"/>
+      <c r="G23" s="26" t="n"/>
+      <c r="H23" s="26" t="n"/>
+    </row>
+    <row r="24" ht="117" customHeight="1">
+      <c r="A24" s="23" t="inlineStr">
         <is>
           <t>机构与订阅</t>
         </is>
       </c>
-      <c r="B21" s="24" t="inlineStr">
+      <c r="B24" s="24" t="inlineStr">
         <is>
           <t>订阅订单能不能删</t>
         </is>
       </c>
-      <c r="C21" s="23" t="inlineStr">
+      <c r="C24" s="23" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -2282,28 +2640,28 @@
           </r>
         </is>
       </c>
-      <c r="D21" s="25" t="inlineStr">
+      <c r="D24" s="25" t="inlineStr">
         <is>
           <t>（1）平台超管</t>
         </is>
       </c>
-      <c r="E21" s="26" t="n"/>
-      <c r="F21" s="26" t="n"/>
-      <c r="G21" s="26" t="n"/>
-      <c r="H21" s="26" t="n"/>
-    </row>
-    <row r="22" ht="145" customHeight="1">
-      <c r="A22" s="23" t="inlineStr">
+      <c r="E24" s="26" t="n"/>
+      <c r="F24" s="26" t="n"/>
+      <c r="G24" s="26" t="n"/>
+      <c r="H24" s="26" t="n"/>
+    </row>
+    <row r="25" ht="145" customHeight="1">
+      <c r="A25" s="23" t="inlineStr">
         <is>
           <t>机构与订阅</t>
         </is>
       </c>
-      <c r="B22" s="24" t="inlineStr">
+      <c r="B25" s="24" t="inlineStr">
         <is>
           <t>配额分两种算法</t>
         </is>
       </c>
-      <c r="C22" s="23" t="inlineStr">
+      <c r="C25" s="23" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -2346,43 +2704,196 @@
           </r>
         </is>
       </c>
-      <c r="D22" s="25" t="inlineStr">
+      <c r="D25" s="25" t="inlineStr">
         <is>
           <t>（1）平台超管
 （2）机构后台</t>
         </is>
       </c>
-      <c r="E22" s="26" t="n"/>
-      <c r="F22" s="26" t="n"/>
-      <c r="G22" s="26" t="n"/>
-      <c r="H22" s="26" t="n"/>
-    </row>
-    <row r="23" ht="22" customHeight="1">
-      <c r="A23" s="27" t="inlineStr">
+      <c r="E25" s="26" t="n"/>
+      <c r="F25" s="26" t="n"/>
+      <c r="G25" s="26" t="n"/>
+      <c r="H25" s="26" t="n"/>
+    </row>
+    <row r="26" ht="130.5" customHeight="1">
+      <c r="A26" s="23" t="inlineStr">
+        <is>
+          <t>机构与订阅</t>
+        </is>
+      </c>
+      <c r="B26" s="24" t="inlineStr">
+        <is>
+          <t>机构用量看板的指标怎么放</t>
+        </is>
+      </c>
+      <c r="C26" s="23" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="10"/>
+            </rPr>
+            <t>（1）放置原则：区间板块放</t>
+          </r>
+          <r>
+            <rPr>
+              <b val="1"/>
+              <color rgb="00DC2626"/>
+              <sz val="10"/>
+            </rPr>
+            <t>流量指标</t>
+          </r>
+          <r>
+            <rPr>
+              <sz val="10"/>
+            </rPr>
+            <t>（时间段内发生的量，随时间筛选联动），实时板块放</t>
+          </r>
+          <r>
+            <rPr>
+              <b val="1"/>
+              <color rgb="00DC2626"/>
+              <sz val="10"/>
+            </rPr>
+            <t>存量指标</t>
+          </r>
+          <r>
+            <rPr>
+              <sz val="10"/>
+            </rPr>
+            <t>（当前 / 累计快照，不随筛选变化）。
+（2）区间运营分析原「商业化与 LLM 消耗」一张卡拆两张：
+商业化卡：区间 GMV、净 GMV（扣退款）、付费用户、付费转化率、永享订单、退款金额、退款率；
+LLM 消耗卡：Token 消耗量、调用次数、平均响应。
+（3）实时板块「用户存量」卡更名「用户与营收存量」，新增</t>
+          </r>
+          <r>
+            <rPr>
+              <b val="1"/>
+              <color rgb="00DC2626"/>
+              <sz val="10"/>
+            </rPr>
+            <t>累计 GMV</t>
+          </r>
+          <r>
+            <rPr>
+              <sz val="10"/>
+            </rPr>
+            <t>（开业以来累计存量）。
+（4）指标口径与机构后台数据看板、功能清单附表三方一致。</t>
+          </r>
+        </is>
+      </c>
+      <c r="D26" s="25" t="inlineStr">
+        <is>
+          <t>（1）平台超管</t>
+        </is>
+      </c>
+      <c r="E26" s="26" t="n"/>
+      <c r="F26" s="26" t="n"/>
+      <c r="G26" s="26" t="n"/>
+      <c r="H26" s="26" t="n"/>
+    </row>
+    <row r="27" ht="117" customHeight="1">
+      <c r="A27" s="23" t="inlineStr">
+        <is>
+          <t>机构与订阅</t>
+        </is>
+      </c>
+      <c r="B27" s="24" t="inlineStr">
+        <is>
+          <t>微信配置补两个上传入口</t>
+        </is>
+      </c>
+      <c r="C27" s="23" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="10"/>
+            </rPr>
+            <t>（1）微信公众号卡片新增「域名校验文件」上传（MP_verify_xxx.txt，公众号后台生成），需放置于网页授权域名</t>
+          </r>
+          <r>
+            <rPr>
+              <b val="1"/>
+              <color rgb="00DC2626"/>
+              <sz val="10"/>
+            </rPr>
+            <t>根目录</t>
+          </r>
+          <r>
+            <rPr>
+              <sz val="10"/>
+            </rPr>
+            <t>下。
+（2）该校验文件属</t>
+          </r>
+          <r>
+            <rPr>
+              <b val="1"/>
+              <color rgb="00DC2626"/>
+              <sz val="10"/>
+            </rPr>
+            <t>公众平台（公众号）的要求</t>
+          </r>
+          <r>
+            <rPr>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">；微信开放平台网站应用（扫码登录）不需要校验文件，开放平台卡片不变。
+（3）微信支付卡片新增「商户 API 私钥」上传（apiclient_key.pem），与商户证书 apiclient_cert.pem </t>
+          </r>
+          <r>
+            <rPr>
+              <b val="1"/>
+              <color rgb="00DC2626"/>
+              <sz val="10"/>
+            </rPr>
+            <t>成对上传</t>
+          </r>
+          <r>
+            <rPr>
+              <sz val="10"/>
+            </rPr>
+            <t>，用于 APIv3 请求签名。</t>
+          </r>
+        </is>
+      </c>
+      <c r="D27" s="25" t="inlineStr">
+        <is>
+          <t>（1）平台超管</t>
+        </is>
+      </c>
+      <c r="E27" s="26" t="n"/>
+      <c r="F27" s="26" t="n"/>
+      <c r="G27" s="26" t="n"/>
+      <c r="H27" s="26" t="n"/>
+    </row>
+    <row r="28" ht="22" customHeight="1">
+      <c r="A28" s="27" t="inlineStr">
         <is>
           <t>■ 权限与角色</t>
         </is>
       </c>
-      <c r="B23" s="27" t="n"/>
-      <c r="C23" s="27" t="n"/>
-      <c r="D23" s="27" t="n"/>
-      <c r="E23" s="27" t="n"/>
-      <c r="F23" s="27" t="n"/>
-      <c r="G23" s="27" t="n"/>
-      <c r="H23" s="27" t="n"/>
-    </row>
-    <row r="24" ht="117" customHeight="1">
-      <c r="A24" s="28" t="inlineStr">
+      <c r="B28" s="27" t="n"/>
+      <c r="C28" s="27" t="n"/>
+      <c r="D28" s="27" t="n"/>
+      <c r="E28" s="27" t="n"/>
+      <c r="F28" s="27" t="n"/>
+      <c r="G28" s="27" t="n"/>
+      <c r="H28" s="27" t="n"/>
+    </row>
+    <row r="29" ht="117" customHeight="1">
+      <c r="A29" s="28" t="inlineStr">
         <is>
           <t>权限与角色</t>
         </is>
       </c>
-      <c r="B24" s="29" t="inlineStr">
+      <c r="B29" s="29" t="inlineStr">
         <is>
           <t>Prompt 编辑权限的从属关系</t>
         </is>
       </c>
-      <c r="C24" s="28" t="inlineStr">
+      <c r="C29" s="28" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -2423,42 +2934,42 @@
           </r>
         </is>
       </c>
-      <c r="D24" s="30" t="inlineStr">
+      <c r="D29" s="30" t="inlineStr">
         <is>
           <t>（1）平台超管</t>
         </is>
       </c>
-      <c r="E24" s="31" t="n"/>
-      <c r="F24" s="31" t="n"/>
-      <c r="G24" s="31" t="n"/>
-      <c r="H24" s="31" t="n"/>
-    </row>
-    <row r="25" ht="22" customHeight="1">
-      <c r="A25" s="32" t="inlineStr">
+      <c r="E29" s="31" t="n"/>
+      <c r="F29" s="31" t="n"/>
+      <c r="G29" s="31" t="n"/>
+      <c r="H29" s="31" t="n"/>
+    </row>
+    <row r="30" ht="22" customHeight="1">
+      <c r="A30" s="32" t="inlineStr">
         <is>
           <t>■ 导出与兑换码</t>
         </is>
       </c>
-      <c r="B25" s="32" t="n"/>
-      <c r="C25" s="32" t="n"/>
-      <c r="D25" s="32" t="n"/>
-      <c r="E25" s="32" t="n"/>
-      <c r="F25" s="32" t="n"/>
-      <c r="G25" s="32" t="n"/>
-      <c r="H25" s="32" t="n"/>
-    </row>
-    <row r="26" ht="117" customHeight="1">
-      <c r="A26" s="33" t="inlineStr">
+      <c r="B30" s="32" t="n"/>
+      <c r="C30" s="32" t="n"/>
+      <c r="D30" s="32" t="n"/>
+      <c r="E30" s="32" t="n"/>
+      <c r="F30" s="32" t="n"/>
+      <c r="G30" s="32" t="n"/>
+      <c r="H30" s="32" t="n"/>
+    </row>
+    <row r="31" ht="117" customHeight="1">
+      <c r="A31" s="33" t="inlineStr">
         <is>
           <t>导出与兑换码</t>
         </is>
       </c>
-      <c r="B26" s="34" t="inlineStr">
+      <c r="B31" s="34" t="inlineStr">
         <is>
           <t>列表导出怎么做</t>
         </is>
       </c>
-      <c r="C26" s="33" t="inlineStr">
+      <c r="C31" s="33" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -2500,29 +3011,29 @@
           </r>
         </is>
       </c>
-      <c r="D26" s="35" t="inlineStr">
+      <c r="D31" s="35" t="inlineStr">
         <is>
           <t>（1）机构后台
 （2）平台超管</t>
         </is>
       </c>
-      <c r="E26" s="36" t="n"/>
-      <c r="F26" s="36" t="n"/>
-      <c r="G26" s="36" t="n"/>
-      <c r="H26" s="36" t="n"/>
-    </row>
-    <row r="27" ht="117" customHeight="1">
-      <c r="A27" s="33" t="inlineStr">
+      <c r="E31" s="36" t="n"/>
+      <c r="F31" s="36" t="n"/>
+      <c r="G31" s="36" t="n"/>
+      <c r="H31" s="36" t="n"/>
+    </row>
+    <row r="32" ht="117" customHeight="1">
+      <c r="A32" s="33" t="inlineStr">
         <is>
           <t>导出与兑换码</t>
         </is>
       </c>
-      <c r="B27" s="34" t="inlineStr">
+      <c r="B32" s="34" t="inlineStr">
         <is>
           <t>兑换码的时间窗与失败提示</t>
         </is>
       </c>
-      <c r="C27" s="33" t="inlineStr">
+      <c r="C32" s="33" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -2548,16 +3059,108 @@
           </r>
         </is>
       </c>
-      <c r="D27" s="35" t="inlineStr">
+      <c r="D32" s="35" t="inlineStr">
         <is>
           <t>（1）机构后台
 （2）移动端</t>
         </is>
       </c>
-      <c r="E27" s="36" t="n"/>
-      <c r="F27" s="36" t="n"/>
-      <c r="G27" s="36" t="n"/>
-      <c r="H27" s="36" t="n"/>
+      <c r="E32" s="36" t="n"/>
+      <c r="F32" s="36" t="n"/>
+      <c r="G32" s="36" t="n"/>
+      <c r="H32" s="36" t="n"/>
+    </row>
+    <row r="33" ht="22" customHeight="1">
+      <c r="A33" s="37" t="inlineStr">
+        <is>
+          <t>■ 登录与验证码</t>
+        </is>
+      </c>
+      <c r="B33" s="37" t="n"/>
+      <c r="C33" s="37" t="n"/>
+      <c r="D33" s="37" t="n"/>
+      <c r="E33" s="37" t="n"/>
+      <c r="F33" s="37" t="n"/>
+      <c r="G33" s="37" t="n"/>
+      <c r="H33" s="37" t="n"/>
+    </row>
+    <row r="34" ht="130.5" customHeight="1">
+      <c r="A34" s="38" t="inlineStr">
+        <is>
+          <t>登录与验证码</t>
+        </is>
+      </c>
+      <c r="B34" s="39" t="inlineStr">
+        <is>
+          <t>短信收不到时的语音兜底</t>
+        </is>
+      </c>
+      <c r="C34" s="38" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="10"/>
+            </rPr>
+            <t>（1）覆盖 C 端全部短信验证码场景：</t>
+          </r>
+          <r>
+            <rPr>
+              <b val="1"/>
+              <color rgb="00DC2626"/>
+              <sz val="10"/>
+            </rPr>
+            <t>登录、绑定手机号、换绑手机号</t>
+          </r>
+          <r>
+            <rPr>
+              <sz val="10"/>
+            </rPr>
+            <t>三处。
+（2）发送短信后 60 秒倒计时结束仍未输入验证码，输入框下方出现次级入口「未收到短信验证码？接听语音电话获取」。
+（3）</t>
+          </r>
+          <r>
+            <rPr>
+              <b val="1"/>
+              <color rgb="00DC2626"/>
+              <sz val="10"/>
+            </rPr>
+            <t>点击即拨打</t>
+          </r>
+          <r>
+            <rPr>
+              <sz val="10"/>
+            </rPr>
+            <t>，不加确认弹窗；入口原地变为状态行「语音电话拨打中 · 来电以 95013 开头，请留意接听」，等待期间常驻。
+（4）60 秒后状态行变为「未接到电话？再次拨打」，可重试。
+（5）语音验证码与短信验证码</t>
+          </r>
+          <r>
+            <rPr>
+              <b val="1"/>
+              <color rgb="00DC2626"/>
+              <sz val="10"/>
+            </rPr>
+            <t>共用同一校验逻辑</t>
+          </r>
+          <r>
+            <rPr>
+              <sz val="10"/>
+            </rPr>
+            <t>。
+（6）「95013」为原型演示号段，实际外呼号段以供应商分配为准，上线前替换文案。</t>
+          </r>
+        </is>
+      </c>
+      <c r="D34" s="40" t="inlineStr">
+        <is>
+          <t>（1）移动端</t>
+        </is>
+      </c>
+      <c r="E34" s="41" t="n"/>
+      <c r="F34" s="41" t="n"/>
+      <c r="G34" s="41" t="n"/>
+      <c r="H34" s="41" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
